--- a/data/trans_bre/P12_1_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P12_1_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,22</t>
+          <t>1,33; 10,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 12,73</t>
+          <t>3,28; 12,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 7,08</t>
+          <t>-0,58; 6,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 13,94</t>
+          <t>0,26; 13,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,08; 117,74</t>
+          <t>10,02; 118,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,68; 155,22</t>
+          <t>26,03; 150,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 130,66</t>
+          <t>-9,47; 127,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 421,81</t>
+          <t>-5,69; 446,87</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 9,16</t>
+          <t>0,93; 9,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,67</t>
+          <t>2,6; 10,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 6,36</t>
+          <t>-0,69; 6,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 5,92</t>
+          <t>-3,93; 6,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 73,96</t>
+          <t>5,9; 75,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,27; 90,71</t>
+          <t>15,55; 91,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 86,21</t>
+          <t>-6,25; 85,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,95; 92,07</t>
+          <t>-33,26; 98,03</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 8,43</t>
+          <t>-0,36; 8,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 12,76</t>
+          <t>3,03; 12,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 6,43</t>
+          <t>-0,34; 6,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,9</t>
+          <t>1,07; 8,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 52,71</t>
+          <t>-2,41; 53,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,48; 85,03</t>
+          <t>17,13; 83,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 84,74</t>
+          <t>-3,21; 82,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 92,87</t>
+          <t>7,47; 92,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 10,0</t>
+          <t>-0,35; 9,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 18,36</t>
+          <t>8,58; 18,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 5,45</t>
+          <t>-2,72; 5,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 14,98</t>
+          <t>2,53; 15,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 66,61</t>
+          <t>-2,53; 64,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,68; 141,29</t>
+          <t>47,53; 144,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 44,57</t>
+          <t>-16,45; 43,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,75; 319,73</t>
+          <t>16,51; 294,34</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 11,78</t>
+          <t>0,05; 12,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 14,17</t>
+          <t>2,9; 14,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 13,9</t>
+          <t>3,85; 14,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 9,08</t>
+          <t>1,59; 9,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 65,34</t>
+          <t>0,37; 66,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 81,5</t>
+          <t>13,5; 86,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,54; 134,39</t>
+          <t>24,75; 135,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 57,08</t>
+          <t>7,72; 58,28</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,11; 15,86</t>
+          <t>3,39; 15,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 19,52</t>
+          <t>6,22; 19,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,02; 13,44</t>
+          <t>1,88; 12,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,8; 64,19</t>
+          <t>4,03; 65,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,52; 108,17</t>
+          <t>16,77; 107,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,5; 157,18</t>
+          <t>29,83; 160,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,32; 118,93</t>
+          <t>10,46; 117,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,74; 474,22</t>
+          <t>23,65; 472,76</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 6,98</t>
+          <t>-7,24; 8,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 20,01</t>
+          <t>5,47; 20,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 16,22</t>
+          <t>2,57; 16,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,75</t>
+          <t>3,93; 13,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 33,07</t>
+          <t>-24,7; 37,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,86; 108,54</t>
+          <t>19,31; 114,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,51; 104,25</t>
+          <t>11,57; 101,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,4; 77,72</t>
+          <t>15,77; 77,01</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,31</t>
+          <t>3,65; 7,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,07</t>
+          <t>8,3; 12,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,67</t>
+          <t>3,23; 6,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,59; 25,63</t>
+          <t>5,45; 26,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,77; 45,95</t>
+          <t>20,35; 46,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,25; 80,52</t>
+          <t>48,74; 79,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,82; 62,09</t>
+          <t>25,75; 61,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,47; 225,35</t>
+          <t>40,26; 231,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_1_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P12_1_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>121,46%</t>
+          <t>152,48%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 10,01</t>
+          <t>1,29; 9,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,49</t>
+          <t>3,3; 12,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 6,91</t>
+          <t>-0,86; 7,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 13,94</t>
+          <t>1,55; 14,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,02; 118,88</t>
+          <t>7,24; 110,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,03; 150,76</t>
+          <t>25,81; 159,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 127,1</t>
+          <t>-9,55; 134,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 446,87</t>
+          <t>5,47; 487,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,1</t>
+          <t>0,38; 8,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,86</t>
+          <t>1,95; 10,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 6,45</t>
+          <t>-0,67; 6,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 6,22</t>
+          <t>-2,51; 6,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 75,14</t>
+          <t>1,69; 68,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,55; 91,04</t>
+          <t>12,34; 91,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 85,8</t>
+          <t>-5,99; 88,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 98,03</t>
+          <t>-20,02; 93,67</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 8,43</t>
+          <t>-0,41; 8,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 12,31</t>
+          <t>3,79; 12,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 6,21</t>
+          <t>-0,61; 6,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,69</t>
+          <t>2,41; 9,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 53,58</t>
+          <t>-1,9; 52,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,13; 83,75</t>
+          <t>19,35; 83,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 82,1</t>
+          <t>-5,27; 82,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 92,34</t>
+          <t>19,06; 116,68</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 9,94</t>
+          <t>-0,12; 9,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 18,53</t>
+          <t>7,89; 17,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,36</t>
+          <t>-2,75; 5,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 15,81</t>
+          <t>1,06; 8,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 64,01</t>
+          <t>-0,09; 63,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,53; 144,16</t>
+          <t>43,09; 130,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 43,83</t>
+          <t>-17,02; 41,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,51; 294,34</t>
+          <t>6,28; 66,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 12,01</t>
+          <t>-0,69; 11,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 14,54</t>
+          <t>2,67; 14,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 14,24</t>
+          <t>4,09; 14,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,24</t>
+          <t>1,43; 9,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 66,06</t>
+          <t>-3,09; 61,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,5; 86,0</t>
+          <t>11,7; 86,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,75; 135,78</t>
+          <t>27,1; 133,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 58,28</t>
+          <t>6,65; 60,16</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32,04</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>206,89%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,84</t>
+          <t>3,7; 16,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 19,51</t>
+          <t>5,96; 19,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 12,77</t>
+          <t>1,87; 13,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,03; 65,39</t>
+          <t>1,4; 9,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,77; 107,31</t>
+          <t>17,39; 111,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,83; 160,73</t>
+          <t>30,75; 154,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,46; 117,24</t>
+          <t>9,39; 112,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,65; 472,76</t>
+          <t>7,26; 72,44</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,64</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 8,02</t>
+          <t>-8,17; 7,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,47; 20,19</t>
+          <t>5,57; 21,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 16,18</t>
+          <t>2,49; 15,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 13,62</t>
+          <t>3,83; 13,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 37,6</t>
+          <t>-28,51; 38,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,31; 114,76</t>
+          <t>20,9; 118,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,57; 101,35</t>
+          <t>10,62; 99,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,77; 77,01</t>
+          <t>15,97; 76,66</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,42</t>
+          <t>3,38; 7,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,3; 12,04</t>
+          <t>8,25; 12,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,68</t>
+          <t>3,24; 6,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,45; 26,46</t>
+          <t>4,48; 7,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,35; 46,14</t>
+          <t>19,08; 46,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,74; 79,47</t>
+          <t>49,0; 82,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,75; 61,27</t>
+          <t>25,82; 61,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,26; 231,53</t>
+          <t>31,34; 62,27</t>
         </is>
       </c>
     </row>
